--- a/docs/tools/Sail-话术卡待确认清单.xlsx
+++ b/docs/tools/Sail-话术卡待确认清单.xlsx
@@ -572,7 +572,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>8 个问题。这些的答案会改变话术怎么写，不只是填空。A1 最重要。</t>
+          <t>9 个问题。这些的答案会改变话术怎么写，不只是填空。A1 最重要。</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -883,6 +883,29 @@
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr"/>
+    </row>
+    <row r="10" ht="112" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>A9</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>单区客人的「最低接单额」定多少？</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>工具 3-3 新增：单区客人（只做一个空间）报价从 RM 3,900（电视柜）到 RM 18,500（厨房）。但一个 RM 3,900 的单要走量尺 → 出图 → 出厂 → 安装一整套流程，占用的是跟 RM 47,948 那单同一批人。没有这条线，业务员会把时间花在结构上就不赚钱的单上 —— 而「逼单」最常发生的正是这里。</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>建议 RM 8,000。低于这个数不是不接，是用便宜的方式接：不出效果图、不约展厅、只报标准款、量尺与安装并单排期。给我一个数字我填进分流表；写 blank 我就把这条删掉。</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
